--- a/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/定義名.xlsx
+++ b/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/定義名.xlsx
@@ -9,8 +9,8 @@
     <x:definedName name="main_cell">sales_data!$E$1</x:definedName>
     <x:definedName name="main_range">sales_data!$E$1:$F$2</x:definedName>
     <x:definedName name="total">sales_data!$B$3</x:definedName>
-    <x:definedName name="local_cell">sales_data!$A$2</x:definedName>
-    <x:definedName name="local_range">sales_data!$A$2:$B$3</x:definedName>
+    <x:definedName name="local_cell" localSheetId="0">sales_data!$A$2</x:definedName>
+    <x:definedName name="local_range" localSheetId="0">sales_data!$A$2:$B$3</x:definedName>
   </x:definedNames>
 </x:workbook>
 </file>

--- a/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/定義名.xlsx
+++ b/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/定義名.xlsx
@@ -9,6 +9,7 @@
     <x:definedName name="main_cell">sales_data!$E$1</x:definedName>
     <x:definedName name="main_range">sales_data!$E$1:$F$2</x:definedName>
     <x:definedName name="total">sales_data!$B$3</x:definedName>
+    <x:definedName name="total" localSheetId="0">sales_data!$B$4</x:definedName>
     <x:definedName name="local_cell" localSheetId="0">sales_data!$A$2</x:definedName>
     <x:definedName name="local_range" localSheetId="0">sales_data!$A$2:$B$3</x:definedName>
   </x:definedNames>
